--- a/files/MainInformationDF.xlsx
+++ b/files/MainInformationDF.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">Description</t>
   </si>
@@ -29,49 +29,49 @@
     <t xml:space="preserve">Timespan</t>
   </si>
   <si>
-    <t xml:space="preserve">1972:2024</t>
+    <t xml:space="preserve">1971:2025</t>
   </si>
   <si>
     <t xml:space="preserve">Sources (Journals, Books, etc)</t>
   </si>
   <si>
-    <t xml:space="preserve">602</t>
+    <t xml:space="preserve">877</t>
   </si>
   <si>
     <t xml:space="preserve">Documents</t>
   </si>
   <si>
-    <t xml:space="preserve">3248</t>
+    <t xml:space="preserve">3597</t>
   </si>
   <si>
     <t xml:space="preserve">Annual Growth Rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62</t>
+    <t xml:space="preserve">1.29</t>
   </si>
   <si>
     <t xml:space="preserve">Document Average Age</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64</t>
+    <t xml:space="preserve">10.3</t>
   </si>
   <si>
     <t xml:space="preserve">Average citations per doc</t>
   </si>
   <si>
-    <t xml:space="preserve">21.13</t>
+    <t xml:space="preserve">20.41</t>
   </si>
   <si>
     <t xml:space="preserve">Average citations per year per doc</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82</t>
+    <t xml:space="preserve">1.675</t>
   </si>
   <si>
     <t xml:space="preserve">References</t>
   </si>
   <si>
-    <t xml:space="preserve">77376</t>
+    <t xml:space="preserve">88330</t>
   </si>
   <si>
     <t xml:space="preserve">DOCUMENT TYPES</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">article</t>
   </si>
   <si>
-    <t xml:space="preserve">2994</t>
+    <t xml:space="preserve">3104</t>
   </si>
   <si>
     <t xml:space="preserve">biographical-item</t>
@@ -92,40 +92,52 @@
     <t xml:space="preserve">book chapter</t>
   </si>
   <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
     <t xml:space="preserve">book review</t>
   </si>
   <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">correction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discussion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">editorial material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">editorial material; early access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">letter</t>
+  </si>
+  <si>
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">correction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">discussion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">editorial material</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">letter; early access</t>
-  </si>
-  <si>
     <t xml:space="preserve">meeting abstract</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
+    <t xml:space="preserve">6</t>
   </si>
   <si>
     <t xml:space="preserve">note</t>
   </si>
   <si>
-    <t xml:space="preserve">11</t>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proceeding paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210</t>
   </si>
   <si>
     <t xml:space="preserve">reprint</t>
@@ -143,13 +155,13 @@
     <t xml:space="preserve">Keywords Plus (ID)</t>
   </si>
   <si>
-    <t xml:space="preserve">3980</t>
+    <t xml:space="preserve">4302</t>
   </si>
   <si>
     <t xml:space="preserve">Author's Keywords (DE)</t>
   </si>
   <si>
-    <t xml:space="preserve">5684</t>
+    <t xml:space="preserve">6521</t>
   </si>
   <si>
     <t xml:space="preserve">AUTHORS</t>
@@ -158,19 +170,19 @@
     <t xml:space="preserve">Authors</t>
   </si>
   <si>
-    <t xml:space="preserve">8307</t>
+    <t xml:space="preserve">9526</t>
   </si>
   <si>
     <t xml:space="preserve">Author Appearances</t>
   </si>
   <si>
-    <t xml:space="preserve">12740</t>
+    <t xml:space="preserve">14171</t>
   </si>
   <si>
     <t xml:space="preserve">Authors of single-authored docs</t>
   </si>
   <si>
-    <t xml:space="preserve">163</t>
+    <t xml:space="preserve">188</t>
   </si>
   <si>
     <t xml:space="preserve">AUTHORS COLLABORATION</t>
@@ -179,25 +191,25 @@
     <t xml:space="preserve">Single-authored docs</t>
   </si>
   <si>
-    <t xml:space="preserve">180</t>
+    <t xml:space="preserve">209</t>
   </si>
   <si>
     <t xml:space="preserve">Documents per Author</t>
   </si>
   <si>
-    <t xml:space="preserve">0.391</t>
+    <t xml:space="preserve">0.378</t>
   </si>
   <si>
     <t xml:space="preserve">Co-Authors per Doc</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92</t>
+    <t xml:space="preserve">3.94</t>
   </si>
   <si>
     <t xml:space="preserve">International co-authorships %</t>
   </si>
   <si>
-    <t xml:space="preserve">12.65</t>
+    <t xml:space="preserve">13.65</t>
   </si>
 </sst>
 </file>
@@ -635,39 +647,39 @@
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -675,7 +687,7 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -699,39 +711,39 @@
         <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -739,23 +751,23 @@
         <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -771,23 +783,23 @@
         <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -808,9 +820,25 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
         <v>3</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B38" t="s">
         <v>3</v>
       </c>
     </row>

--- a/files/MainInformationDF.xlsx
+++ b/files/MainInformationDF.xlsx
@@ -29,25 +29,25 @@
     <t xml:space="preserve">Timespan</t>
   </si>
   <si>
-    <t xml:space="preserve">1971:2025</t>
+    <t xml:space="preserve">1971:2024</t>
   </si>
   <si>
     <t xml:space="preserve">Sources (Journals, Books, etc)</t>
   </si>
   <si>
-    <t xml:space="preserve">877</t>
+    <t xml:space="preserve">770</t>
   </si>
   <si>
     <t xml:space="preserve">Documents</t>
   </si>
   <si>
-    <t xml:space="preserve">3597</t>
+    <t xml:space="preserve">3464</t>
   </si>
   <si>
     <t xml:space="preserve">Annual Growth Rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29</t>
+    <t xml:space="preserve">11.99</t>
   </si>
   <si>
     <t xml:space="preserve">Document Average Age</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">Average citations per doc</t>
   </si>
   <si>
-    <t xml:space="preserve">20.41</t>
+    <t xml:space="preserve">20.74</t>
   </si>
   <si>
     <t xml:space="preserve">Average citations per year per doc</t>
   </si>
   <si>
-    <t xml:space="preserve">1.675</t>
+    <t xml:space="preserve">1.696</t>
   </si>
   <si>
     <t xml:space="preserve">References</t>
   </si>
   <si>
-    <t xml:space="preserve">88330</t>
+    <t xml:space="preserve">84633</t>
   </si>
   <si>
     <t xml:space="preserve">DOCUMENT TYPES</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">article</t>
   </si>
   <si>
-    <t xml:space="preserve">3104</t>
+    <t xml:space="preserve">3044</t>
   </si>
   <si>
     <t xml:space="preserve">biographical-item</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">book chapter</t>
   </si>
   <si>
-    <t xml:space="preserve">17</t>
+    <t xml:space="preserve">14</t>
   </si>
   <si>
     <t xml:space="preserve">book review</t>
@@ -104,6 +104,9 @@
     <t xml:space="preserve">correction</t>
   </si>
   <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
     <t xml:space="preserve">discussion</t>
   </si>
   <si>
@@ -113,15 +116,15 @@
     <t xml:space="preserve">editorial material</t>
   </si>
   <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
     <t xml:space="preserve">editorial material; early access</t>
   </si>
   <si>
     <t xml:space="preserve">letter</t>
   </si>
   <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
     <t xml:space="preserve">meeting abstract</t>
   </si>
   <si>
@@ -131,13 +134,10 @@
     <t xml:space="preserve">note</t>
   </si>
   <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
     <t xml:space="preserve">proceeding paper</t>
   </si>
   <si>
-    <t xml:space="preserve">210</t>
+    <t xml:space="preserve">146</t>
   </si>
   <si>
     <t xml:space="preserve">reprint</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">review</t>
   </si>
   <si>
-    <t xml:space="preserve">207</t>
+    <t xml:space="preserve">205</t>
   </si>
   <si>
     <t xml:space="preserve">DOCUMENT CONTENTS</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">Keywords Plus (ID)</t>
   </si>
   <si>
-    <t xml:space="preserve">4302</t>
+    <t xml:space="preserve">4214</t>
   </si>
   <si>
     <t xml:space="preserve">Author's Keywords (DE)</t>
   </si>
   <si>
-    <t xml:space="preserve">6521</t>
+    <t xml:space="preserve">6173</t>
   </si>
   <si>
     <t xml:space="preserve">AUTHORS</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">Authors</t>
   </si>
   <si>
-    <t xml:space="preserve">9526</t>
+    <t xml:space="preserve">9124</t>
   </si>
   <si>
     <t xml:space="preserve">Author Appearances</t>
   </si>
   <si>
-    <t xml:space="preserve">14171</t>
+    <t xml:space="preserve">13704</t>
   </si>
   <si>
     <t xml:space="preserve">Authors of single-authored docs</t>
   </si>
   <si>
-    <t xml:space="preserve">188</t>
+    <t xml:space="preserve">171</t>
   </si>
   <si>
     <t xml:space="preserve">AUTHORS COLLABORATION</t>
@@ -191,25 +191,25 @@
     <t xml:space="preserve">Single-authored docs</t>
   </si>
   <si>
-    <t xml:space="preserve">209</t>
+    <t xml:space="preserve">191</t>
   </si>
   <si>
     <t xml:space="preserve">Documents per Author</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378</t>
+    <t xml:space="preserve">0.38</t>
   </si>
   <si>
     <t xml:space="preserve">Co-Authors per Doc</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94</t>
+    <t xml:space="preserve">3.96</t>
   </si>
   <si>
     <t xml:space="preserve">International co-authorships %</t>
   </si>
   <si>
-    <t xml:space="preserve">13.65</t>
+    <t xml:space="preserve">13.48</t>
   </si>
 </sst>
 </file>
@@ -663,55 +663,55 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">

--- a/files/MainInformationDF.xlsx
+++ b/files/MainInformationDF.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t xml:space="preserve">Description</t>
   </si>
@@ -35,19 +35,19 @@
     <t xml:space="preserve">Sources (Journals, Books, etc)</t>
   </si>
   <si>
-    <t xml:space="preserve">770</t>
+    <t xml:space="preserve">741</t>
   </si>
   <si>
     <t xml:space="preserve">Documents</t>
   </si>
   <si>
-    <t xml:space="preserve">3464</t>
+    <t xml:space="preserve">3429</t>
   </si>
   <si>
     <t xml:space="preserve">Annual Growth Rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">11.99</t>
+    <t xml:space="preserve">11.98</t>
   </si>
   <si>
     <t xml:space="preserve">Document Average Age</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">Average citations per doc</t>
   </si>
   <si>
-    <t xml:space="preserve">20.74</t>
+    <t xml:space="preserve">20.82</t>
   </si>
   <si>
     <t xml:space="preserve">Average citations per year per doc</t>
   </si>
   <si>
-    <t xml:space="preserve">1.696</t>
+    <t xml:space="preserve">1.704</t>
   </si>
   <si>
     <t xml:space="preserve">References</t>
   </si>
   <si>
-    <t xml:space="preserve">84633</t>
+    <t xml:space="preserve">83334</t>
   </si>
   <si>
     <t xml:space="preserve">DOCUMENT TYPES</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">article</t>
   </si>
   <si>
-    <t xml:space="preserve">3044</t>
+    <t xml:space="preserve">3021</t>
   </si>
   <si>
     <t xml:space="preserve">biographical-item</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">book chapter</t>
   </si>
   <si>
-    <t xml:space="preserve">14</t>
+    <t xml:space="preserve">13</t>
   </si>
   <si>
     <t xml:space="preserve">book review</t>
@@ -125,6 +125,9 @@
     <t xml:space="preserve">letter</t>
   </si>
   <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">meeting abstract</t>
   </si>
   <si>
@@ -134,10 +137,13 @@
     <t xml:space="preserve">note</t>
   </si>
   <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
     <t xml:space="preserve">proceeding paper</t>
   </si>
   <si>
-    <t xml:space="preserve">146</t>
+    <t xml:space="preserve">135</t>
   </si>
   <si>
     <t xml:space="preserve">reprint</t>
@@ -155,13 +161,13 @@
     <t xml:space="preserve">Keywords Plus (ID)</t>
   </si>
   <si>
-    <t xml:space="preserve">4214</t>
+    <t xml:space="preserve">4163</t>
   </si>
   <si>
     <t xml:space="preserve">Author's Keywords (DE)</t>
   </si>
   <si>
-    <t xml:space="preserve">6173</t>
+    <t xml:space="preserve">6071</t>
   </si>
   <si>
     <t xml:space="preserve">AUTHORS</t>
@@ -170,19 +176,19 @@
     <t xml:space="preserve">Authors</t>
   </si>
   <si>
-    <t xml:space="preserve">9124</t>
+    <t xml:space="preserve">9001</t>
   </si>
   <si>
     <t xml:space="preserve">Author Appearances</t>
   </si>
   <si>
-    <t xml:space="preserve">13704</t>
+    <t xml:space="preserve">13568</t>
   </si>
   <si>
     <t xml:space="preserve">Authors of single-authored docs</t>
   </si>
   <si>
-    <t xml:space="preserve">171</t>
+    <t xml:space="preserve">170</t>
   </si>
   <si>
     <t xml:space="preserve">AUTHORS COLLABORATION</t>
@@ -191,13 +197,13 @@
     <t xml:space="preserve">Single-authored docs</t>
   </si>
   <si>
-    <t xml:space="preserve">191</t>
+    <t xml:space="preserve">190</t>
   </si>
   <si>
     <t xml:space="preserve">Documents per Author</t>
   </si>
   <si>
-    <t xml:space="preserve">0.38</t>
+    <t xml:space="preserve">0.381</t>
   </si>
   <si>
     <t xml:space="preserve">Co-Authors per Doc</t>
@@ -209,7 +215,7 @@
     <t xml:space="preserve">International co-authorships %</t>
   </si>
   <si>
-    <t xml:space="preserve">13.48</t>
+    <t xml:space="preserve">13.44</t>
   </si>
 </sst>
 </file>
@@ -695,36 +701,36 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
@@ -732,15 +738,15 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -748,23 +754,23 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
@@ -772,31 +778,31 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
@@ -804,34 +810,34 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38">

--- a/files/MainInformationDF.xlsx
+++ b/files/MainInformationDF.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">Description</t>
   </si>
@@ -35,43 +35,43 @@
     <t xml:space="preserve">Sources (Journals, Books, etc)</t>
   </si>
   <si>
-    <t xml:space="preserve">759</t>
+    <t xml:space="preserve">844</t>
   </si>
   <si>
     <t xml:space="preserve">Documents</t>
   </si>
   <si>
-    <t xml:space="preserve">3508</t>
+    <t xml:space="preserve">3637</t>
   </si>
   <si>
     <t xml:space="preserve">Annual Growth Rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78</t>
+    <t xml:space="preserve">9.84</t>
   </si>
   <si>
     <t xml:space="preserve">Document Average Age</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74</t>
+    <t xml:space="preserve">11</t>
   </si>
   <si>
     <t xml:space="preserve">Average citations per doc</t>
   </si>
   <si>
-    <t xml:space="preserve">20.71</t>
+    <t xml:space="preserve">20.59</t>
   </si>
   <si>
     <t xml:space="preserve">Average citations per year per doc</t>
   </si>
   <si>
-    <t xml:space="preserve">1.776</t>
+    <t xml:space="preserve">1.554</t>
   </si>
   <si>
     <t xml:space="preserve">References</t>
   </si>
   <si>
-    <t xml:space="preserve">84119</t>
+    <t xml:space="preserve">87631</t>
   </si>
   <si>
     <t xml:space="preserve">DOCUMENT TYPES</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">article</t>
   </si>
   <si>
-    <t xml:space="preserve">3098</t>
+    <t xml:space="preserve">3170</t>
   </si>
   <si>
     <t xml:space="preserve">biographical-item</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">book chapter</t>
   </si>
   <si>
-    <t xml:space="preserve">13</t>
+    <t xml:space="preserve">15</t>
   </si>
   <si>
     <t xml:space="preserve">book review</t>
@@ -113,12 +113,15 @@
     <t xml:space="preserve">editorial material</t>
   </si>
   <si>
-    <t xml:space="preserve">15</t>
+    <t xml:space="preserve">17</t>
   </si>
   <si>
     <t xml:space="preserve">letter</t>
   </si>
   <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
     <t xml:space="preserve">letter; early access</t>
   </si>
   <si>
@@ -131,13 +134,13 @@
     <t xml:space="preserve">note</t>
   </si>
   <si>
-    <t xml:space="preserve">12</t>
+    <t xml:space="preserve">16</t>
   </si>
   <si>
     <t xml:space="preserve">proceeding paper</t>
   </si>
   <si>
-    <t xml:space="preserve">138</t>
+    <t xml:space="preserve">179</t>
   </si>
   <si>
     <t xml:space="preserve">reprint</t>
@@ -146,7 +149,7 @@
     <t xml:space="preserve">review</t>
   </si>
   <si>
-    <t xml:space="preserve">211</t>
+    <t xml:space="preserve">214</t>
   </si>
   <si>
     <t xml:space="preserve">DOCUMENT CONTENTS</t>
@@ -155,13 +158,13 @@
     <t xml:space="preserve">Keywords Plus (ID)</t>
   </si>
   <si>
-    <t xml:space="preserve">4232</t>
+    <t xml:space="preserve">4361</t>
   </si>
   <si>
     <t xml:space="preserve">Author's Keywords (DE)</t>
   </si>
   <si>
-    <t xml:space="preserve">6234</t>
+    <t xml:space="preserve">6547</t>
   </si>
   <si>
     <t xml:space="preserve">AUTHORS</t>
@@ -170,19 +173,19 @@
     <t xml:space="preserve">Authors</t>
   </si>
   <si>
-    <t xml:space="preserve">9258</t>
+    <t xml:space="preserve">9610</t>
   </si>
   <si>
     <t xml:space="preserve">Author Appearances</t>
   </si>
   <si>
-    <t xml:space="preserve">13957</t>
+    <t xml:space="preserve">14232</t>
   </si>
   <si>
     <t xml:space="preserve">Authors of single-authored docs</t>
   </si>
   <si>
-    <t xml:space="preserve">168</t>
+    <t xml:space="preserve">184</t>
   </si>
   <si>
     <t xml:space="preserve">AUTHORS COLLABORATION</t>
@@ -191,25 +194,25 @@
     <t xml:space="preserve">Single-authored docs</t>
   </si>
   <si>
-    <t xml:space="preserve">187</t>
+    <t xml:space="preserve">206</t>
   </si>
   <si>
     <t xml:space="preserve">Documents per Author</t>
   </si>
   <si>
-    <t xml:space="preserve">0.379</t>
+    <t xml:space="preserve">0.378</t>
   </si>
   <si>
     <t xml:space="preserve">Co-Authors per Doc</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98</t>
+    <t xml:space="preserve">3.91</t>
   </si>
   <si>
     <t xml:space="preserve">International co-authorships %</t>
   </si>
   <si>
-    <t xml:space="preserve">0.02851</t>
+    <t xml:space="preserve">0.0275</t>
   </si>
 </sst>
 </file>
@@ -663,7 +666,7 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -687,12 +690,12 @@
         <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -700,47 +703,47 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -748,23 +751,23 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
         <v>3</v>
@@ -772,31 +775,31 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
         <v>3</v>
@@ -804,34 +807,34 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38">
